--- a/docs/harness/wirelist/A-engine-pinouts.xlsx
+++ b/docs/harness/wirelist/A-engine-pinouts.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Flex fuel sensor (fuel return line) pin 3</t>
+          <t>Flex fuel sensor (fuel return line) pin C</t>
         </is>
       </c>
     </row>
@@ -2961,8 +2961,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>1</v>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -2981,8 +2983,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>2</v>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -3001,8 +3005,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>3</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>

--- a/docs/harness/wirelist/A-engine-pinouts.xlsx
+++ b/docs/harness/wirelist/A-engine-pinouts.xlsx
@@ -28,7 +28,7 @@
     <sheet name="IX-B-RAIL inline plug, +5 V to " sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bulkhead BH-A (DRB102, RH firew'!$A$2:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bulkhead BH-A (DRB102, RH firew'!$A$2:$D$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Bulkhead BH-A (DRB102, RH firew'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Turbo speed sensor (turbospd)'!$A$2:$D$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Turbo speed sensor (turbospd)'!$1:$2</definedName>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -609,17 +609,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>w_inj_pwr_e_ae</t>
+          <t>w_cop_pwr_e_ae</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Injector +12 V feed</t>
+          <t>Coil +12 V feed</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>splice sp_inj_eng (Injector +12 V splice)</t>
+          <t>splice sp_cop_eng (Coil +12 V splice)</t>
         </is>
       </c>
     </row>
@@ -629,723 +629,611 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>w_cop_pwr_e_ae</t>
+          <t>w_inj_pwr_e_ae</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Coil +12 V feed</t>
+          <t>Injector +12 V feed</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>splice sp_cop_eng (Coil +12 V splice)</t>
+          <t>splice sp_inj_eng (Injector +12 V splice)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>cab_crank_c1</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Crank sensor signal</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Crank sensor pin 1</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>w2</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Gnd crank sensor</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Crank sensor pin 2</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>cab_crank_sh</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>w_rail_sp_8v_e</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>+8 V to cam sensor</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Cam sensor (Hall) pin 1</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>cab_cam_c2</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Cam sensor (Hall) pin 2</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>w24</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Gnd cam sensor</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Cam sensor (Hall) pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>cab_cam_sh</t>
+          <t>w120_e</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Coil 1 trigger (IGT)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
+          <t>Ignition coil cyl 1 pin 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>w218</t>
+          <t>w121_e</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>+5 V turbo speed</t>
+          <t>Coil 2 trigger (IGT)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Turbo speed sensor pin A</t>
+          <t>Ignition coil cyl 2 pin 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>w16_e</t>
+          <t>w122_e</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Turbo speed signal</t>
+          <t>Coil 3 trigger (IGT)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Turbo speed sensor pin B</t>
+          <t>Ignition coil cyl 3 pin 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>w17</t>
+          <t>w123_e</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Gnd turbo speed</t>
+          <t>Coil 4 trigger (IGT)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Turbo speed sensor pin C</t>
+          <t>Ignition coil cyl 4 pin 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>cab_turbo_sh</t>
+          <t>w_5v_brail_e_c46</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>+5 V fuel pressure</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_e</t>
+          <t>w206</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>+12 V boost + flex</t>
+          <t>+5 V MAP sensor</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>splice sp_sw12_eng (Switched +12 V splice)</t>
+          <t>MAP sensor (sensor block, LH firewall) pin 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>w48_e</t>
+          <t>w26_e</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Flex fuel signal</t>
+          <t>MAP sensor signal</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Flex fuel sensor (fuel return line) pin C</t>
+          <t>MAP sensor (sensor block, LH firewall) pin 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>cab_flex_sh</t>
+          <t>w_gnd_a_e_c44</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Gnd flex + MAP</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
+          <t>splice sp_gndout_eng2 (Sensor return splice)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>w126</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>+5 V throttle sensor</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Throttle body (Bosch ETB) pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>w128_e</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Throttle pos 1 main</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Throttle body (Bosch ETB) pin 6</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>w129_e</t>
+          <t>w108_e</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Throttle pos 2 sub</t>
+          <t>Injector 1 drive (-)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Throttle body (Bosch ETB) pin 5</t>
+          <t>Injector cyl 1 pin 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>w_rail_sp_gndout_e</t>
+          <t>w109_e</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Gnd IAT/TPS/coolant</t>
+          <t>Injector 2 drive (-)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout_eng (Sensor return splice)</t>
+          <t>Injector cyl 2 pin 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>cab_etbs_sh</t>
+          <t>w110_e</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Injector 3 drive (-)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
+          <t>Injector cyl 3 pin 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>w206</t>
+          <t>w111_e</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>+5 V MAP sensor</t>
+          <t>Injector 4 drive (-)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>MAP sensor (sensor block, LH firewall) pin 2</t>
+          <t>Injector cyl 4 pin 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>w_gnd_a_e_c44</t>
+          <t>w_5v_brail_e_c47</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Gnd flex + MAP</t>
+          <t>+5 V coolant press</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>splice sp_gndout_eng2 (Sensor return splice)</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>w26_e</t>
+          <t>w_5v_brail_e_c45</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>MAP sensor signal</t>
+          <t>+5 V oil pressure</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>MAP sensor (sensor block, LH firewall) pin 3</t>
+          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>w108_e</t>
+          <t>w_rail_sp_sw12_e</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Injector 1 drive (-)</t>
+          <t>+12 V boost + flex</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Injector cyl 1 pin 2</t>
+          <t>splice sp_sw12_eng (Switched +12 V splice)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>w109_e</t>
+          <t>w48_e</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Injector 2 drive (-)</t>
+          <t>Flex fuel signal</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Injector cyl 2 pin 2</t>
+          <t>Flex fuel sensor (fuel return line) pin C</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>w110_e</t>
+          <t>cab_flex_sh</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Injector 3 drive (-)</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Injector cyl 3 pin 2</t>
+          <t>cable screen (one end only)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>w111_e</t>
+          <t>w202_e</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Injector 4 drive (-)</t>
+          <t>Intake temp signal</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Injector cyl 4 pin 2</t>
+          <t>Intake air temp sensor (manifold) pin 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>w120_e</t>
+          <t>w_rail_sp_gndout_e</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Coil 1 trigger (IGT)</t>
+          <t>Gnd IAT/TPS/coolant</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Ignition coil cyl 1 pin 3</t>
+          <t>splice sp_gndout_eng (Sensor return splice)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>w121_e</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr"/>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Coil 2 trigger (IGT)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Ignition coil cyl 2 pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>w122_e</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Coil 3 trigger (IGT)</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Ignition coil cyl 3 pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>w123_e</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Coil 4 trigger (IGT)</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Ignition coil cyl 4 pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>w103_e</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Boost solenoid (-)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Boost control solenoid pin 2</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>w201_e</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Coolant temp signal</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Coolant temp sensor (water neck) pin 1</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>w202_e</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Intake temp signal</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Intake air temp sensor (manifold) pin 1</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>w_hv_mrs_en_e</t>
+          <t>w126</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
+          <t>+5 V throttle sensor</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>EHPS PUMP pin C-1</t>
+          <t>Throttle body (Bosch ETB) pin 3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>w_mrs_e</t>
+          <t>w128_e</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>EHPS pump speed</t>
+          <t>Throttle pos 1 main</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>EHPS PUMP pin B-2</t>
+          <t>Throttle body (Bosch ETB) pin 6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B40" s="8" t="inlineStr"/>
       <c r="C40" s="9" t="inlineStr">
@@ -1357,15 +1245,23 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>w129_e</t>
+        </is>
+      </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr"/>
+          <t>Throttle pos 2 sub</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Throttle body (Bosch ETB) pin 5</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
@@ -1373,107 +1269,99 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>w_5v_brail_e_c45</t>
+          <t>cab_etbs_sh</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>+5 V oil pressure</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 1</t>
+          <t>cable screen (one end only)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>w_5v_brail_e_c46</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>+5 V fuel pressure</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 2</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>w_5v_brail_e_c47</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>+5 V coolant press</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine pin 3</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>w218</t>
+        </is>
+      </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
+          <t>+5 V turbo speed</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Turbo speed sensor pin A</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>w16_e</t>
+        </is>
+      </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr"/>
+          <t>Turbo speed signal</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Turbo speed sensor pin B</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>w_eps_rly_e</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>EHPS PUMP pin B-5</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B48" s="8" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
@@ -1485,42 +1373,394 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>w17</t>
+        </is>
+      </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
+          <t>Gnd turbo speed</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Turbo speed sensor pin C</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>cab_turbo_sh</t>
+        </is>
+      </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr"/>
+          <t>Turbo speed shield</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>w103_e</t>
+        </is>
+      </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
+          <t>Boost solenoid (-)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Boost control solenoid pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>w_rail_sp_8v_e</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>+8 V to cam sensor</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Cam sensor (Hall) pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>cab_cam_c2</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Cam sensor signal</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Cam sensor (Hall) pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>w24</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Gnd cam sensor</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Cam sensor (Hall) pin 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>cab_cam_sh</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Cam sensor shield</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>w201_e</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Coolant temp signal</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Coolant temp sensor (water neck) pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>cab_crank_c1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Crank sensor signal</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Crank sensor pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>w2</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Gnd crank sensor</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Crank sensor pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>cab_crank_sh</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Crank sensor shield</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>w_hv_mrs_en_e</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>EHPS enable +12 V</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>EHPS PUMP pin C-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>w_mrs_e</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>EHPS pump speed</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>EHPS PUMP pin B-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>w_eps_rly_e</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>EHPS relay coil (-)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>EHPS PUMP pin B-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>spare, sealing plug</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr"/>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr"/>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr"/>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr"/>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr"/>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D51"/>
+  <autoFilter ref="A2:D71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1618,7 +1858,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 36</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 10</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1981,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 37</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 11</t>
         </is>
       </c>
     </row>
@@ -1864,7 +2104,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 38</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 12</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2195,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall) pin 87</t>
+          <t>Bulkhead BH-B (DRB102, RH firewall) pin 46</t>
         </is>
       </c>
     </row>
@@ -1995,7 +2235,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 23</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 41</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2255,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall) pin 86</t>
+          <t>Bulkhead BH-B (DRB102, RH firewall) pin 45</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2275,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 25</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 44</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2295,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 24</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 42</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2386,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 39</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 58</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2457,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 40</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 70</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2548,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 41</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 33</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2639,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 9</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 74</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2659,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 10</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 75</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2730,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 12</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 63</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2750,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 13</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 64</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2770,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 14</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 65</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2841,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 47</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 27</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2861,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 50</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 13</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2881,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 51</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 25</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2990,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 16</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 52</t>
         </is>
       </c>
     </row>
@@ -2772,7 +3012,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 17</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 53</t>
         </is>
       </c>
     </row>
@@ -2794,7 +3034,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 18</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 56</t>
         </is>
       </c>
     </row>
@@ -2885,7 +3125,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 28</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 16</t>
         </is>
       </c>
     </row>
@@ -2905,7 +3145,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 30</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 17</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3262,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 21</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 31</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3353,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 31</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 21</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3444,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 32</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 22</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3535,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 33</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 23</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3626,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 34</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 24</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3729,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 35</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 9</t>
         </is>
       </c>
     </row>
